--- a/Acoustics/Exam_1_Folder/Crossover_resistors.xlsx
+++ b/Acoustics/Exam_1_Folder/Crossover_resistors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{CA700721-6809-4060-9ADE-DBB539215F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="13372" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-86" yWindow="43" windowWidth="18129" windowHeight="13046" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Crossover_speakers" sheetId="1" r:id="rId1"/>

--- a/Acoustics/Exam_1_Folder/Crossover_resistors.xlsx
+++ b/Acoustics/Exam_1_Folder/Crossover_resistors.xlsx
@@ -3,19 +3,32 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA700721-6809-4060-9ADE-DBB539215F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{CA700721-6809-4060-9ADE-DBB539215F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2F7502A-D959-4377-8E9E-C31043291CC6}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="43" windowWidth="18129" windowHeight="13046" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="13372" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Crossover_speakers" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>DataPtNum</t>
   </si>
@@ -26,9 +39,6 @@
     <t>phase</t>
   </si>
   <si>
-    <t>Gain (|Vin/Vout|)</t>
-  </si>
-  <si>
     <t>Vin(FuncGen)</t>
   </si>
   <si>
@@ -37,11 +47,20 @@
   <si>
     <t>Vout(LoPass)</t>
   </si>
+  <si>
+    <t>Gain HiPass (|Vout/Vin|)</t>
+  </si>
+  <si>
+    <t>Gain LoPass (|Vout/Vin|)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -87,10 +106,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.4609375" customWidth="1"/>
@@ -439,10 +459,11 @@
     <col min="4" max="4" width="11.61328125" customWidth="1"/>
     <col min="5" max="5" width="12.15234375" customWidth="1"/>
     <col min="6" max="6" width="12.3828125" customWidth="1"/>
-    <col min="7" max="8" width="16.3046875" customWidth="1"/>
+    <col min="7" max="7" width="24.23046875" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,22 +471,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -484,8 +508,16 @@
       <c r="F2">
         <v>-1.44</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G2" s="3">
+        <f>D2/C2</f>
+        <v>0.72</v>
+      </c>
+      <c r="H2" s="3">
+        <f>E2/C2</f>
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -504,8 +536,16 @@
       <c r="F3">
         <v>-1.6220000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:G50" si="0">D3/C3</f>
+        <v>0.72</v>
+      </c>
+      <c r="H3" s="3">
+        <f t="shared" ref="H3:H50" si="1">E3/C3</f>
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -524,8 +564,16 @@
       <c r="F4">
         <v>-1.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G4" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -544,8 +592,16 @@
       <c r="F5">
         <v>-1.978</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -564,8 +620,16 @@
       <c r="F6">
         <v>-2.1429999999999998</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -584,8 +648,16 @@
       <c r="F7">
         <v>-7.0129999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -604,8 +676,16 @@
       <c r="F8">
         <v>-7.6059999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G8" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -624,8 +704,16 @@
       <c r="F9">
         <v>-4.0599999999999996</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G9" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -644,8 +732,16 @@
       <c r="F10">
         <v>-4.32</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G10" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -664,8 +760,16 @@
       <c r="F11">
         <v>-1.5249999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -684,8 +788,16 @@
       <c r="F12">
         <v>-1.6220000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -704,8 +816,16 @@
       <c r="F13">
         <v>-1.7</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.71287128712871284</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1881188118811881E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -724,8 +844,16 @@
       <c r="F14">
         <v>-1.8</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.71287128712871284</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3861386138613862E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -744,8 +872,16 @@
       <c r="F15">
         <v>-9.73</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.71287128712871284</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4851485148514851E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -764,8 +900,16 @@
       <c r="F16">
         <v>-10.08</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.71287128712871284</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6831683168316833E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -784,8 +928,16 @@
       <c r="F17">
         <v>-9</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.71287128712871284</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6831683168316833E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -804,8 +956,16 @@
       <c r="F18">
         <v>-14.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.71287128712871284</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0792079207920793E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -824,8 +984,16 @@
       <c r="F19">
         <v>-16.36</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.70588235294117641</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="1"/>
+        <v>2.6470588235294117E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -844,8 +1012,16 @@
       <c r="F20">
         <v>-21.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.69902912621359214</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="1"/>
+        <v>3.2038834951456312E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -864,8 +1040,16 @@
       <c r="F21">
         <v>-23.51</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.68571428571428561</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="1"/>
+        <v>3.8095238095238092E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -884,8 +1068,16 @@
       <c r="F22">
         <v>-24.3</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G22" s="3">
+        <f t="shared" si="0"/>
+        <v>0.69714285714285706</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="1"/>
+        <v>4.8571428571428564E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -904,8 +1096,16 @@
       <c r="F23">
         <v>-28.68</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G23" s="3">
+        <f t="shared" si="0"/>
+        <v>0.69056603773584901</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="1"/>
+        <v>5.6603773584905655E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -924,8 +1124,16 @@
       <c r="F24">
         <v>-31.44</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G24" s="3">
+        <f t="shared" si="0"/>
+        <v>0.6777777777777777</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="1"/>
+        <v>6.5740740740740725E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -944,8 +1152,16 @@
       <c r="F25">
         <v>-31.56</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.67522935779816506</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="1"/>
+        <v>7.5229357798165142E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -964,8 +1180,16 @@
       <c r="F26">
         <v>-31.47</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G26" s="3">
+        <f t="shared" si="0"/>
+        <v>0.67272727272727262</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="1"/>
+        <v>8.7272727272727266E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -984,8 +1208,16 @@
       <c r="F27">
         <v>-38.950000000000003</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G27" s="3">
+        <f t="shared" si="0"/>
+        <v>0.6607142857142857</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="1"/>
+        <v>9.8214285714285712E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1004,8 +1236,16 @@
       <c r="F28">
         <v>-38.880000000000003</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G28" s="3">
+        <f t="shared" si="0"/>
+        <v>0.65263157894736845</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="1"/>
+        <v>0.10964912280701755</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1024,8 +1264,16 @@
       <c r="F29">
         <v>-41.19</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G29" s="3">
+        <f t="shared" si="0"/>
+        <v>0.64482758620689662</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="1"/>
+        <v>0.12155172413793103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1044,8 +1292,16 @@
       <c r="F30">
         <v>-43.78</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G30" s="3">
+        <f t="shared" si="0"/>
+        <v>0.63389830508474576</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="1"/>
+        <v>0.13389830508474576</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1064,8 +1320,16 @@
       <c r="F31">
         <v>-46.28</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.62333333333333341</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="1"/>
+        <v>0.14833333333333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1084,8 +1348,16 @@
       <c r="F32">
         <v>-48.6</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G32" s="3">
+        <f t="shared" si="0"/>
+        <v>0.61639344262295082</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="1"/>
+        <v>0.16065573770491803</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1104,8 +1376,16 @@
       <c r="F33">
         <v>-67.91</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G33" s="3">
+        <f t="shared" si="0"/>
+        <v>0.51914893617021274</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.30070921985815602</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1124,8 +1404,16 @@
       <c r="F34">
         <v>-87.84</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G34" s="3">
+        <f t="shared" si="0"/>
+        <v>0.42191780821917807</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="1"/>
+        <v>0.43287671232876712</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1144,8 +1432,16 @@
       <c r="F35">
         <v>-99</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G35" s="3">
+        <f t="shared" si="0"/>
+        <v>0.3309352517985612</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="1"/>
+        <v>0.52949640287769784</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1164,8 +1460,16 @@
       <c r="F36">
         <v>-110.6</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G36" s="3">
+        <f t="shared" si="0"/>
+        <v>0.265625</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="1"/>
+        <v>0.59687500000000004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1184,8 +1488,16 @@
       <c r="F37">
         <v>-117.1</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G37" s="3">
+        <f t="shared" si="0"/>
+        <v>0.21186440677966104</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="1"/>
+        <v>0.65423728813559323</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1204,8 +1516,16 @@
       <c r="F38">
         <v>-125.3</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G38" s="3">
+        <f t="shared" si="0"/>
+        <v>0.17321428571428571</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="1"/>
+        <v>0.69285714285714284</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1224,8 +1544,16 @@
       <c r="F39">
         <v>-128.1</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G39" s="3">
+        <f t="shared" si="0"/>
+        <v>0.14339622641509434</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="1"/>
+        <v>0.73207547169811316</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1244,8 +1572,16 @@
       <c r="F40">
         <v>-138.6</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G40" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12038834951456311</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="1"/>
+        <v>0.73786407766990292</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1264,8 +1600,16 @@
       <c r="F41">
         <v>-135</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G41" s="3">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" si="1"/>
+        <v>0.73725490196078425</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1284,8 +1628,16 @@
       <c r="F42">
         <v>-141.19999999999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G42" s="3">
+        <f t="shared" si="0"/>
+        <v>8.5685483870967749E-2</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="1"/>
+        <v>0.75806451612903225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1304,8 +1656,16 @@
       <c r="F43">
         <v>-141.4</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G43" s="3">
+        <f t="shared" si="0"/>
+        <v>7.3770491803278687E-2</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="1"/>
+        <v>0.77049180327868849</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1324,8 +1684,16 @@
       <c r="F44">
         <v>-144.1</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G44" s="3">
+        <f t="shared" si="0"/>
+        <v>6.4049586776859499E-2</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="1"/>
+        <v>0.76859504132231404</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1344,8 +1712,16 @@
       <c r="F45">
         <v>-147.4</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G45" s="3">
+        <f t="shared" si="0"/>
+        <v>5.7773109243697482E-2</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="1"/>
+        <v>0.78151260504201681</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1364,8 +1740,16 @@
       <c r="F46">
         <v>-145.4</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G46" s="3">
+        <f t="shared" si="0"/>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="1"/>
+        <v>0.78813559322033899</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1384,8 +1768,16 @@
       <c r="F47">
         <v>-144.9</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G47" s="3">
+        <f t="shared" si="0"/>
+        <v>4.6610169491525424E-2</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="1"/>
+        <v>0.78813559322033899</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1404,8 +1796,16 @@
       <c r="F48">
         <v>-150.80000000000001</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G48" s="3">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="1"/>
+        <v>0.79487179487179482</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1424,8 +1824,16 @@
       <c r="F49">
         <v>-141.69999999999999</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G49" s="3">
+        <f t="shared" si="0"/>
+        <v>3.8793103448275856E-2</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" si="1"/>
+        <v>0.79741379310344818</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1443,6 +1851,14 @@
       </c>
       <c r="F50">
         <v>-142.30000000000001</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="0"/>
+        <v>3.9130434782608692E-2</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999993</v>
       </c>
     </row>
   </sheetData>
